--- a/new/261018.xlsx
+++ b/new/261018.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D0B9A9-0C45-4509-A837-94CDADE8D17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED749497-181D-41A1-900E-65BC6C082131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="4110" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9880" yWindow="4110" windowWidth="15010" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
-    <sheet name="SheetX" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="SheetX" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>每周采访-160904-Kolner</t>
   </si>
@@ -199,6 +200,225 @@
 sehr schnell erkennt, dass Protektionismus keine Dauerlösung ist, sondern letztlich Weltoffenheit, wenn es darum geht, Innovationen
 ist dann eben nicht geregelt.
 Und deswegen bin ich nach wie vor dafür</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>und dann spätestens im März, nächsten Jahres in Rom zu beiden großen Themenblöcken verbindliche Entscheidungen für die Mitgliedstaaten und für die europäischen Gremien schaffen werden.
+Riedel: Offen und ehrlich wollte man miteinander reden.
+Sie haben schon gesagt, Sie sehen auch Bewegung in der Flüchtlingsfrage.
+Darüber hat man aber doch im Grunde - als ein Thema, wo schon mal klar war, dass es da krachen würde - gar nicht besonders ausführlich gesprochen.
+Woher nehmen Sie die Ansicht, dass sich da was bewegt?
+Oettinger: Es geht zum einen um die Frage: Wie vermindern wir Fluchtgründe der Zukunft.
+Und hier der weitere Ausbau unserer gemeinsamen europäischen Entwicklungshilfe und Nachbarschaftspolitik ist, glaube ich, der eine wichtige Punkt.
+Der zweite ist, dass es ja viele Flüchtlinge in Europa, namentlich in Deutschland gibt.
+Hier glaube ich nicht daran, dass die Verteilungs-Quote mit weit mehr als 100.000 Flüchtlingen in den nächsten Monaten umgesetzt wird.
+Deswegen geht es um die Frage einer sogenannten Flexibilität.
+Die muss nur glaubwürdig sein und darf die Regeln der Solidarität nicht verletzen.
+Das heißt, wenn ein Mitgliedsstaat partout nicht bereit ist, entlang der Quote einige Tausend Flüchtlinge aufzunehmen, dann muss er eine vergleichbare Aufgabe wahrnehmen und entweder Soldaten und Sicherheitskräfte, oder auch soziale Dienste an die Außengrenzen schicken und damit Frontex stärken.
+Oder er muss Geld geben.
+Riedel: Das ist das Konzept der " flexiblen Solidarität" , das die Visegrád-Gruppe eingebracht hat.
+Es passt ja auch ein bisschen zu dem, was EU-Kommissionspräsident Juncker diese Woche in Straßburg in seiner Rede zur Lage der Union gesagt hat, wo er davon sprach, dass man Solidarität nicht erzwingen kann, sondern diese freiwillig sein müsste.
+Auf der anderen Seite würde es natürlich auch bedeuten, wenn man darauf einginge, dass man darauf verzichtet, dass Beschlossenes, Verabredetes auch umgesetzt werden muss.
+Oettinger: Gleichwertigkeit von Leistungen ist wichtig Oettinger: Deswegen ist ist mir die Gleichwertigkeit von Leistungen wichtig.
+Noch mal - aus vielen Gesprächen mit ungarischen Vertretern, mit polnischen Vertretern, mit slowakischen Vertretern weiß ich, dass dort auch entlang ihrer eigenen Geschichte die Aufnahme von namentlich muslimischen Flüchtlingen in größere Zahl überhaupt keine Akzeptanz hat.
+Übrigens auch Frankreich, Präsident Hollande, der ansonsten sehr kooperativ ist, hat keinen Spielraum, so sagt er, weil ansonsten die Rechtspopulisten in den Umfragen weiter nach oben ziehen.
+Wenn dem so ist, dann muss man prüfen, wo diese Länder ohne in der Innenpolitik unzumutbare Probleme zu bekommen, durch Fachkräfte, durch Soldaten, durch soziale Dienste, durch Geld helfen und damit für alle Mitgliedsstaaten und alle Bürger in ganz Europa die Solidarität gewährt wird.
+Riedel: Das heißt aber auch, dass man dem Rechtspopulismus nachgeben würde.
+Oettinger: Dass man ihn erkennen muss und dass man dort, wo er billige Argumente sucht, ihm diese billigen Argumente nicht geben darf.
+Riedel: Die Bundeskanzlerin hat nach dem Treffen von Bratislava einen " Geist von Bratislava" ausmachen wollen.
+Welches ist dieser Geist von Bratislava aus Ihrer Sicht?
+Ein neuer Realismus und nicht Wolkenkuckucksheime bauen wollen?
+Oettinger: Die erste Gefahr scheint gebannt, dass der Brexit zu einer Blaupause für andere Länder wird.
+Jetzt wird man sehen, wie die Rechtspopulisten im nächsten Jahr in Frankreich, auch in Deutschland, in den Niederlanden auftreten, wie sie dann in Österreich auftreten.
+Aber ich glaube, die Staats- und Regierungschefs und Herr Tusk und Herr Juncker werden alles tun, um die Gemeinschaft der 27 Mitgliedsstaaten zu erhalten.
+Zum Zweiten, es gibt Aufgabenbereiche, da macht mehr Europa Sinn.
+In der Außen- und Sicherheitspolitik macht Europa viel Sinn.
+Bei digitalen Strategien macht Europa viel Sinn.
+Und andererseits müssen wir in Brüssel sehen: Wo ist im Augenblick die Bereitschaft zur Vertiefung Europas nicht gegeben, wo müssen wir Vielfalt akzeptieren, vielleicht auch mehrere Geschwindigkeiten akzeptieren.
+Ich glaube, es muss ein Prozess sein, der mit guten Argumenten dort Europa vertieft, wo es Europa und allen Mitgliedsstaaten hilft.
+Und dort den Mitgliedsstaaten Zeit gibt und Freiraum gibt, wo sie ihn brauchen.
+Riedel: Dann wäre der Geist von Bratislava ein sich Konzentrieren auf das Machbare und nicht das Denkbare oder gar das Wünschbare?
+Oettinger: Ja.
+Europa wird sich nicht im Jahre 2016/2017 völlig verändern.
+Es geht darum, das Erreichte zu erhalten.
+Ich bin gerade außerhalb von Europa, ich bin in New York.
+Egal, wo ich bin - die Zusammenarbeit der Europäischen Union gilt als ein wunderbares Vorbild.
+Kein anderer Kontinent arbeitet zwischen so vielen Religionen, Geschichte, Kulturen und schrecklichen Kriegen so gut zusammen bei allen Gegensätzen, wie die Multikultur Europas.
+Das zu erhalten, es auch offensiv zu vertreten, es auch in Bildern - und sei es nur auf der Donau auf einem Schiff zu zeigen -, dafür einen neuen Mitgliedsstaat und eine kleine Hauptstadt, Bratislava, als Ort zu nehmen - all dies sind, glaube ich, gute Zeichen, die der Bürger begreift.
+Riedel: In der Erklärung von Bratislava heißt es, Zitat: Zwar ist die EU nicht fehlerfrei, aber sie ist das beste Instrument, über das wir verfügen.
+Und dann heißt es da auch noch: Wir benötigen sie.
+Und genannt wird dann: Frieden und Demokratie und Sicherheit und Wohlstand und in Europa frei leben, studieren, arbeiten und reisen zu können.
+Das ist ja auch mal etwas Neues, das so etwas betont wird.
+Erwarten Sie, dass alle, die dieses Papier jetzt mit verabschiedet haben, das dann auch zu Hause vertreten, sich dann noch daran erinnern, wenn sie das nächste Mal zu Hause in ihren Nationen, in ihren Hauptstädten über die EU reden?
+Oettinger: Bei der Kanzlerin bin ich mir sicher, dass sie es in Berlin oder auch in Kiel oder Stuttgart genauso wie in Bratislava oder Brüssel oder Luxemburg vertreten wird.
+Riedel: Ja, aber ein Herr Orbán beispielsweise oder eine Frau Szydlo aus Polen machen das möglicherweise nicht?
+Oettinger: Deswegen müssen wir sehr aufpassen.
+Wir lesen ja die Zeitungen von Budapest, von Warschau, von Krakau.
+Und wir hören ja auch, was im Parlament gesagt wird.
+Und deswegen sollten wir dort, wo zweigleisig gefahren wird, wo man im europäischen Team europäisch ist und zu Hause populistisch, das nicht mehr hinnehmen.
+Ich glaube, da sind auch ganz klare mahnende Worte im Einzelfall durch europäische Vertreter gefragt.
+Riedel: Mahnende Worte sind dann vielleicht ein etwas schwaches Mittel – und andere hat man ja aber nicht.
+Oettinger: Das stimmt.
+Aber der Bürger in diesen Ländern, der hört und sieht ja auch was läuft.
+Wenn der sieht, dass sein Regierungschef in Bratislava Gemeinsamkeiten betont, unterschreibt und dann gegebenenfalls zu Hause das Gegenteil tut: Auf Dauer ist dieser Spagat nicht glaubwürdig und ich glaube auch nicht erfolgreich.
+Riedel: Jetzt heißt es in der Erklärung von Bratislava auch: Eine Vision einer attraktiven EU soll aufgezeigt werden.
+Und zwar bis Mitte März, bis Rom, wenn der 60.
+Geburtstag der Römischen Verträge gefeiert wird und damit sozusagen die Geburtsstunde der EU. Was ist Ihre Vision einer attraktiven EU?
+Oettinger: Vision von einer einheitlichen Stimme nach außen Oettinger: Meine Vision ist, dass sie nach außen mit einer Stimme spricht in Sachen Syrien und dem Bürgerkrieg, in Sachen Ägypten, in Sachen Libyen, in Sachen Mali, Niger.
+Riedel: Also eine europäische Außenministerin?
+Oettinger: Eine mehr und mehr kohärente, gemeinsame Außenpolitik quasi, ja.
+Wenn wir 28 Stimmen haben, haben wir in allen Sitzungssälen der Welt keine Autorität.
+Nehmen Sie einmal das Thema Klimaschutz.
+Im letzten Jahr war Paris, da hatten wir ein gemeinsames Konzept und waren erfolgreich.
+Wir sind noch immer als Europäer gemeinsam stark genug, um die Welt von morgen mitzugestalten.
+28 Mitgliedsstaaten alleine, auch Deutschland alleine, sind auf Dauer nicht wahrnehmbar.
+Riedel: Es war ja in der Tat einer der Vorschläge von EU-Kommissionspräsident Juncker letzte Woche in Straßburg, dass er – wir haben bisher eine Außenbeauftragte, Federica Mogherini – eine echte Außenministerin aus ihr machen möchte.
+Aber ist das nicht schon fast eine erste Vision in diesem Zusammenhang, wo man sich schwer vorstellen kann, dass sich die 27 darauf wirklich einigen?
+Gäben doch auch Paris, auch Berlin eine ganz wichtige nationale Kompetenz, nämlich die Außenpolitik, ab und würden sie nicht nur punktuell an verschiedenen Stellen in verschiedenen Formaten bündeln?
+Oettinger: Das Ganze ist ein Prozess.
+Da kann man nichts von heute auf morgen und 180 Grad umsteuern.
+Als ich vor sieben Jahren von Stuttgart nach Brüssel kam, gab es praktisch keine gemeinsame Außenpolitik.
+Durch den Vertrag von Lissabon haben wir jetzt die Hohe Beauftragte, haben einen Auswärtigen Dienst.
+Das heißt, in den letzten sieben Jahren wurde einiges erreicht.
+Frau Mogherini sitzt auch überall zwischen den führenden Köpfen aus Washington D.C., aus Moskau.
+Und ich glaube, auch die großen Mitgliedsstaaten akzeptieren von Jahr zu Jahr mehr, dass man nach außen durch Frau Mogherini und durch die Kommission mit einer Stimme auftreten.
+Riedel: Und Sie sind davon überzeugt, dass man entscheidende Schritte in diese Richtung tatsächlich bis zum nächsten März gemacht haben kann, dass es dann ein gemeinsames Bild – um nicht noch mal Vision zu sagen –, ein gemeinsames Bild, was diese 27 sein sollen, von der EU geben kann?
+Oettinger: Die Chance ist da.
+Übrigens, so sehr ich bedaure, dass die Briten sich mit knapper Mehrheit für den Ausstieg entschieden haben, ein Gutes hat es: Die Briten waren in allen Fragen der Zusammenarbeit von Geheimdiensten, von Polizeien, von Europol, von gemeinsamer Verteidigungs- und auch Außenpolitik sehr, sehr defensiv, haben alle Fortschritte nicht akzeptiert.
+Da ist die Bereitschaft von Paris und Berlin viel weitergehend, da werden sich die kleinen Mitgliedsstaaten anschließen.
+Das heißt, hier könnte der Weggang von Großbritannien sogar einen Schub geben.
+Riedel: Der Brexit als Chance?
+Oettinger: Briten waren immer im Bremserhaus Oettinger: Nochmals, ich bedaure diesen Schritt – warten wir ab, wie es dann bis 2019 weitergeht.
+Aber bei diesen großen Fragen, bei denen Bratislava jetzt einen Auftrag erteilt hat, ist die Zusammenarbeit der 27 viel leichter als die zwischen allen 28.
+Das heißt, die Briten waren hier immer im Bremserhaus.
+Riedel: Wer sind eigentlich die Verbündeten – wenn es darum geht, sich ein Bild von dieser EU der 27 zu zimmern – der Deutschen?
+Im Vorfeld von Bratislava hatten sich ja nicht nur die Visegrád-Gruppe organisiert und formiert mit ihren Vorstellungen – da haben wir schon drüber gesprochen –, sondern auch die Südeuropäer inklusive der gewichtigen Ländern Frankreich und Italien.
+Die wollen mehr Ausgaben für Wachstum und weniger Sparpolitik.
+Und das passt nicht mit den Vorstellungen Deutschlands zusammen.
+Wer zieht mit Deutschland an einem Strang?
+Oettinger: Das hängt von den Themen und den Feldern der Politik ab.
+In der Außenpolitik, bei den großen Linien ist es unverändert Frankreich, vielleicht kommt Italien hinzu.
+Und im Bereich der europäischen Haushaltspolitik in der Eurozone sind es die Letten, die Litauer und die Esten, die Finnen und die Holländer und da sind die Mittelmehranrainer eher anderer Position.
+Insoweit gibt es nicht die Verbündeten für alle Fragen.
+Es gibt Aufgabengebiete, in denen haben wir mehr, in anderen haben wir weniger, in den einen haben wir die Einen, in den anderen die Anderen als Partner.
+Aber das Gewicht Deutschlands im Rat ist immer noch stark genug, um nicht übergangen zu werden.
+Riedel: Ist es nicht so, dass aufgrund dieser Tatsache, aber auch, wenn man in der Verteidigungspolitik strukturiert enger zusammenarbeiten will, wo nicht alle dabei sein können oder nicht alle dabei sein wollen – das ist möglich vertraglich, dass eine Zahl X einfach beschließt, bei bestimmten Themen zusammen zu arbeiten –, läuft das nicht dann doch, stärker als bisher auch schon, auf ein Europa der verschiedenen Geschwindigkeiten, der verschiedenen Integrationstiefen zu?
+Oettinger: Das hatten wir bisher schon.
+Riedel: Eben, aber noch mehr davon.
+Oettinger: Man sollte nicht am Anfang auf dem Langsamsten warten Oettinger: Das war bei der Währung so.
+Das war bei Schengen so, das wird es immer bei Themenfeldern geben.
+Aber eines sollte das Ziel sein: dass am Ende die anderen nachkommen.
+Das heißt, wir dürfen nicht die Geschwindigkeiten auf Dauer unterschiedlich gestalten.
+Es können einige vorangehen, vielleicht mit der Finanztransaktionssteuer zehn, elf Ländern – wird man sehen.
+Bei Schengen war es der Fall, aber die anderen kamen dann im Laufe der Jahre nach.
+Die Eurozone wurde mit weit weniger Ländern gestartet, die drei Balten kamen nach als Beispiel.
+Ich baue darauf, dass auch die Polen mal nachkommen, die Ungarn mal nachkommen.
+Es muss immer am Ende Kohärenz geben, aber man sollte nicht am Anfang auf den Langsamsten und Letzten warten müssen.
+Riedel: Sie hören das Interview der Woche, heute mit Günter Oettinger, EU-Kommissar für Digitale Wirtschaft und Gesellschaft.
+Besser kommunizieren, Herr Oettinger, will man untereinander – so ist es beschlossen – und mit den Bürgern – so heißt es auch in der Bratislava-Erklärung.
+Was einen Vorschlag aus Ihrem Haus angeht, muss man zumindest von einem kommunikativen GAU sprechen - Stichwort Roaming-Gebühren.
+Sie abzuschaffen, das war eines der Vorzeigeprojekte, mit denen man ja gerade die Bürger wieder für den Gedanken der EU und ihren praktischen Nutzen gewinnen wollte, sie es spüren lassen wollte.
+Es ist auch beschlossen und verkündet: keine Gebühren mehr für mobiles Telefonieren bei Aufenthalten im Ausland.
+Aber jetzt hat die EU-Kommission den Auftrag gehabt, noch sogenannte Fairness-Klauseln einzubauen.
+Die wurden vorgestellt, vor knapp zwei Wochen, und kaum vorgestellt, wieder zurückgezogen, weil es einen Aufschrei der Empörung gab: Nur 90 Tage pro Jahr, nur 30 Tage am Stück, sollte ohne Roaming-Gebühren im EU-Ausland telefoniert werden können.
+Haben Sie diesen Entwurf für diese Klausel nicht vorher gesehen oder nicht vorhergesehen, was für einen Sturm der Kritik es hageln würde?
+Oettinger: Der Vorschlag wurde mit verschiedenen Dienststellen erarbeitet, wurde von allen gesehen.
+Und ein Argument war: Mit 90 Tagen decken wir die Urlaubs- und Dienstreisen von 99 Prozent aller europäischen Bürger ab.
+Riedel: Aber zum Beispiel nicht die Erasmus-Studenten, die für mehrere Monate in einem europäischen Land sind.
+Oettinger: Das stimmt.
+Deswegen sagte ich ja: 99 Prozent.
+Was ist denn der Hintergrund?
+Wir haben nicht den Telefonmarkt Europas und nicht den Telefonpreis.
+Die Letten bezahlen ein Siebtel der Iren.
+Und deswegen müssen wir Missbrauch verhindert.
+Sie könnten, wenn wir das falsch konzipieren, in Dublin leben, mit einem Telefonoperator in Lettland einen Vertrag schließen, aber immer von Dublin aus telefonieren – der wäre innerhalb von wenigen Tagen insolvent.
+Riedel: Aber warum wäre das so ein Drama, wenn sich dann die billigsten Anbieter durchsetzen?
+Oettinger: Neuer Vorschlag zum Roaming Oettinger: Nein, die Billigsten gingen Konkurs, das ist das Problem.
+Weil die Billigsten dann im Großhandelsmarkt von der Telefonie Dublin-Lettland/Lettland-Dublin höhere Preise bezahlen müssten, als sie selbst vor Ort für ihre SIM-Karte verlangen können.
+Das heißt, wir müssen hier Rücksicht nehmen auf die ganz starken Unterschiede in den einzelnen Telefonmärkten.
+Deswegen werden wir jetzt einen Weg vorschlagen, der diese Kontrolle - wo ist jemand, wo ist ein Erstwohnsitz, wo hält er sich auf - vornimmt.
+Das macht aber mehr Kontrolle notwendig und der Vorschlag wird nächste Woche beraten werden.
+Riedel: Und wie kann man so etwas kontrollieren?
+Oettinger: Gute Frage – wir arbeiten daran.
+Riedel: Ein Punkt des Fahrplans von Bratislava, Herr Oettinger, nachdem bestimmte konkrete Projekte jetzt umgesetzt werden sollen – Sie haben die Stichworte am Anfang schon genannte – und auch ein wichtiger Teil des Arbeitsprogramms der EU-Kommission ist die Entwicklung des Digitalen Binnenmarktes – Ihre Domäne.
+Sie haben passend zu Junckers Aufschlag noch am Tag der Rede letzte Wochen in Straßburg konkrete Vorschläge dazu vorgestellt, wie etwa der Telekommunikationsmarkt neu geregelt werden kann und die Gesetzgebung zum Urheberrecht aktualisiert werden kann.
+Jenseits der Wirtschaftsseiten ist das etwas untergegangen, wegen der Rede.
+War das Timing optimal?
+Warum haben Sie das nicht auch kommende Woche vorgestellt?
+Oettinger: Wir sehen den Zeitdruck, weil in den nächsten zwei, drei Jahren eine Reihe von neuen Telekommunikationsdiensten kommen wird, die eine völlig neue Infrastruktur benötigen.
+Deswegen haben wir keine Zeit zu verlieren.
+Riedel: Keine Woche?
+Oettinger: Wir waren fertig gewesen.
+Der Termin war lange geplant, den halten wir ein.
+Mir geht es nicht um die Show, mir geht es um die Sache.
+Und ich wollte, dass wir noch in diesem Jahr die Beratungen im Rat und im Parlament beginnen können.
+Und ob ich dann eine Woche später Platz gehabt hätte auf der Tagesordnung, das war unsicher.
+Deswegen habe ich gesagt: Ich gehe zum frühestmöglichen Zeitpunkt hinein.
+Und dann konnten wir ja auch schon am gleichen Tag beweisen, dass die Rede des Präsidenten nicht nur eine Rede ist, sondern auch Fakten, Vorschläge auf den Tisch gelegt werden.
+Worum geht es?
+In der Vergangenheit waren die Telekom-Unternehmen für die Telefonie verantwortlich – Festnetz oder Mobil.
+Aber die ganzen neuen Dienste, wie Telemedizin oder autonomes Fahren oder Industrie 4.0 oder intelligente Stromnetze, die volatile Strommengen aus Solar stabilisieren müssen, das geht nur mir einer völlig neuen Infrastruktur, mit einer Gigabit-Infrastruktur.
+Dafür sind 500 Milliarden Investments notwendig.
+Und dafür schaffen wir jetzt den europäischen Rahmen, dass die in den nächsten Jahren auch ausgerollt werden.
+Im Augenblick ist Südkorea uns weit voraus, andere sind ebenfalls aktiv.
+Und ich will nicht, dass in drei, vier Jahren gesagt wird: Der Europäer haben zwar gute Autobahnen, ordentliche Schienengleise, eine gute Infrastruktur generell, aber im digitalen Sektor haben wir den Vorsprung der anderen nicht gesehen.
+Wir wollen zeitgleich oder früher als andere in die moderne digitale Infrastruktur treten.
+Riedel: Und dafür ist man bereit, notfalls auch eigene Grundsätze, was Wettbewerbsvorstellungen angeht, beiseitezustellen?
+Denn es sieht ja so aus, dass die Telekom-Marktführer das Recht bekommen sollen, sich unter bestimmten Bedingungen, also zum Beispiel im dünn besiedelten ländlichen Raum, beim Netzausbau zusammenzuschließen und Wettbewerber aus den neuen Leitungen auszusperren.
+Das ist ja genau das, was man sonst an jeder Stelle versucht, zu verhindert.
+Oettinger: In dünn besiedelten Gebieten Polens, Rumäniens, auch in Deutschland, laufen wir Gefahr, dass niemand investiert.
+Das Beste wäre, es würden drei investieren - das stimmt.
+Aber bevor drei überlegen und dann nicht Geld ausgeben, lieber ein oder zwei, damit eine Infrastruktur besteht.
+Insoweit ist es eine pragmatische Lösung, die mit allen Beteiligten besprochen wurde.
+Und noch mal, das Ziel muss sein, dass es keine Regionen gibt, die verlieren.
+Der Wert eines Grundstücks oder die Bereitschaft, im ländlichen Raum zu investieren oder als Steuerberater oder als Arzt dort eine Praxis aufzubauen, wird in Zukunft entscheidend von der digitalen Infrastruktur abhängen.
+Deswegen brauchen wir eine flächendeckende gute Infrastruktur, die im Verdichtungsraum zweimal, dreimal, viermal und im ländlichen Raum zumindest einmal.
+Riedel: Heftig Kritik hat es auch gehagelt an den Vorschlägen, was die Reform des Urheberrechts angeht.
+Das sieht – um es mal ganz vereinfacht zu sagen – vor, dass Onlineplattformen, also Google, Google News, Twitter und Co, künftig an Presseverlage zahlen sollen, wenn sie Teile von Presseartikeln veröffentlichen.
+Und die Hauptkritik dabei ist, dass die Großen – also die genannten – ohnehin die Macht haben werden, ihre Lizenzen, die sie dafür erwerben müssen, gratis zu kriegen, einfach, wenn sie damit wedeln, mit der Möglichkeit verweisen, ansonsten eben bestimmte Presseverlage, bestimmte Presseinhalte gar nicht mehr auf ihren Seiten zu haben.
+Und die Verlage sind natürlich darauf angewiesen, dass sie in irgendeiner Form auch zu ihren Nutzern kommen.
+Oettinger: Ansatz ist faire Vergütung für Kreative Oettinger: Also mit Verlaub, da gab es auch viel Beifall dafür.
+Worum geht es im Kern?
+Übrigens, wenn Sie sagen, die Kritik ist sehr einseitig: Die Verleger haben gesagt: Richtig.
+Fragen Sie die Kreativwirtschaft.
+Im Augenblick sind Komponisten, Musiker, Sänger, Journalisten, Buchautoren, Wissenschaftler auf der Verliererseite, weil sie für ihre wertvolle Arbeit im Kreativsektor immer wenige Geld bekommen.
+Und ich will, dass in Europa Künstler, Wissenschaftler, Kreativschaffende überleben und auch eine gute berufliche Perspektive behalten.
+Ich war mit vielen Kreativen in Kontakt, die mich dringend gebeten haben, jetzt etwas zu tun, das von dem, was an Milliarden die Onlineplattformen verdienen, indem sie den Download ermöglichen und auf Ihrem Display Werbung aufscheint, indem davon ein direkter Teil an die Kreativen übergeht – der Ansatz dabei: eine faire Vergütung.
+Wenn Sie hier am Mikrofon nicht mich hätten, sondern Sänger und Komponisten, die würden sagen: endlich, endlich, endlich!
+Riedel: Die Idee ist ja auch nicht schlecht, aber man hat ja gesehen, dass es beispielsweise in Deutschland ...
+Oettinger: Vielen Dank dafür.
+Vielen Dank.
+Riedel: ...
+oder in Spanien, wo es ja schon ein Leistungsschutzgesetzt gibt, dass es eben nicht wirklich funktioniert.
+Weil dann die kleineren Anbieter gezwungen sind, diese Lizenzen zu bezahlen, denen das dann, wenn sie Start-ups sind, eher schadet und die Großen, die haben diese Gratislizenzen.
+Oettinger: Aber genau hier macht Europa den Unterschied.
+Kein Mitgliedsstaat, kein Land, kein Markt alleine hat die Stärke, um die Onlineplattformen dieser Welt zu fairen Vergütungen zu bringen.
+Aber die 510 Millionen Menschen Europas – mit der Schweiz, mit Norwegen und dem Westbalkan assoziiert – sind stark genug, Regeln im Markt durchzusetzen, sofern es Regeln gibt.
+Und die schaffen wir jetzt.
+Riedel: Die EU-Kommission – das sieht man bei diesem Punkt auch wieder ganz gut – ist eigentlich von den Institutionen der EU in der komfortabelsten Situation: Sie stellen Dinge vor – gut, das wird dann auch oft kritisiert –, aber Sie müssen nicht dafür sorgen, dass Sie dann politische Mehrheiten finden und umgesetzt werden.
+Denn Sie brauchen auch für diese Vorschläge – und die werden Sie wahrscheinlich so nicht bekommen – die Zustimmung des Europäischen Parlaments, ganz abgesehen von den EU-Mitgliedsländern.
+Oettinger: Ja, aber das ist doch in Deutschland genau gleich.
+Kein Gesetz ohne Bundestag und Bundesrat.
+Das heißt, die Bundesregierung macht einen Vorschlag und dann beschließt der Bundestag und der Bundesrat.
+Insofern sind wir eine Art Regierung Europas und das Parlament und der Rat sind die beiden Kammern, die dann entscheiden müssen.
+Riedel: Und das gehört zu Ihrer Vision – um darauf zum Schluss noch mal zurückzukommen –, dass irgendwann das Wort " eine Art" wegfällt?
+Oettinger: Wir nennen uns Geschäftsführung Europas.
+Aber mehr und mehr Gesetze erfordern eine Regierung.
+Und deswegen ist die Kommission eine Quasi-Regierung Europas, ja.
+Riedel: Herr Oettinger, ich danke Ihnen für das Gespräch und einen schönen Gruß nach New York.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周采访-260918-Oettinger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">welche Note hat der informelle 27er-Gipfel der EU-Staats- und Regierungschefs aus Ihrer Sicht verdient?
+Günter Oettinger: in zwei großen Bereichen ein klares Arbeitsprogramm auferlegt.
+mehr um den Bereich der Außen- und Sicherheitspolitik, um eine gemeinsame Linie beim Schutz der Außengrenzen.
+Und andererseits geht es um das Thema Standort Europa, Wettbewerbsfähigkeit und vor allen Dingen, wie wir digitale Technologien nutzen.
+Riedel: ist fast schon ein Ausrufungszeichen wert?
+Oettinger: aus der Europäischen Union raus will, niemand so fundamental auftritt, um die anderen massiv zu brüskieren, auch nicht die Visegrád-Staaten.
+Und jetzt wird es sich zeigen, ob wir in der zweiten Hälfte dieses Spiels weitere Tore machen </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -564,28 +784,54 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{681F16E2-351E-42D6-B9A8-44AF4B1D0EDD}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="322" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B42DA9-40FB-4B5C-864C-5AD944C8F030}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="26.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/new/261018.xlsx
+++ b/new/261018.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED749497-181D-41A1-900E-65BC6C082131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D090F02C-FA04-43E2-B2F6-C17B5C1F5AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="4110" windowWidth="15010" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7910" yWindow="2720" windowWidth="15010" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
-    <sheet name="SheetX" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
+    <sheet name="SheetX" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>每周采访-160904-Kolner</t>
   </si>
@@ -419,6 +420,207 @@
 Riedel: ist fast schon ein Ausrufungszeichen wert?
 Oettinger: aus der Europäischen Union raus will, niemand so fundamental auftritt, um die anderen massiv zu brüskieren, auch nicht die Visegrád-Staaten.
 Und jetzt wird es sich zeigen, ob wir in der zweiten Hälfte dieses Spiels weitere Tore machen </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tauber: Also, wir haben uns darum gekümmert, dass wir als CDU – und dazu dienen ja auch die Deutschlandkongresse, die derzeit mit der bayerischen Schwester zusammen stattfinden – programmatisch auf der Höhe der Zeit bleiben.
+Wir haben für die Partei selbst eine Parteireform auf den Weg gebracht – " Meine CDU 2017" –, wo es dann auch um organisatorische und strukturelle Fragen geht, damit wir als Volkspartei nah bei den Menschen bleiben.
+Und wir haben in drei großen Zukunftsthemen die CDU auch programmatisch weiterentwickelt.
+Die CSU hat gerade ein neues Grundsatzprogramm auf den Weg gebracht.
+Also, ich glaube, da sind wir gut unterwegs.
+Detjen: Das war jetzt nicht ganz die Antwort auf die Frage.
+Aber da warten wir ab, wie sich Angela Merkel dann entscheidet und erklärt.
+Herr Tauber, Parteipolitik scheint ohnehin ein ...
+Tauber: Entschuldigung, wenn ich da nochmal einhake.
+Die Partei ist nicht allein die Vorsitzende, sondern wenn Sie nach einer möglichen Verkrustung oder Unbeweglichkeit von Parteien fragen, dann ist für mich als Generalsekretär da vor allem das Programm wichtig.
+Und wir haben in vielen Fragen auch immer wieder neu nachgedacht beim Thema Nachhaltigkeit zum Beispiel, beim Thema Entwicklungs- und Zusammenarbeit und auch eine Partei zu sein, in der Menschen willkommen sind und mitarbeiten können.
+Das ist auch eine wichtige Frage und auch da haben wir uns verändert.
+Detjen: Ja, aber die Frage war natürlich, ob es generell für Parteien gut ist, so lange Amtszeiten zu haben.
+Das ist eine Frage, die stellt sich ja jetzt bei der Abwägung, sowohl für Angela Merkel und auch für Sie, wenn Sie Ihren Wunsch artikulieren.
+Tauber: Also, ich kann für mein Heimatland Hessen sagen, dass es dem Hessenland gutgetan hat, dass wir seit '99 regieren.
+Und ich glaube, auch die Freunde in Bayern werden für sich reklamieren, dass die Regierung der CSU dem Land guttut.
+Also insofern, glaube ich, kommt es nicht allein auf die Dauer der Regierung an, sondern bleibt man auch selbstkritisch, schaut man, was sind die neuen Fragen.
+Und auch da, wie gesagt, das tun wir gerade gemeinsam mit der CSU. Detjen: Sie haben, Herr Tauber, auf Erneuerung in der CDU verwiesen.
+An diesem Wochenende sind Sie damit konfrontiert, dass mehrere Zeitungen unabhängig voneinander über verschiedene Vorfälle von Sexismus und Mobbing in der CDU berichten.
+Das soll sich in Berlin abgespielt haben, da geht es aber auch um Ihren Heimatkreisverband.
+Man kann, wenn man das liest, den Eindruck bekommen, Ihre Partei hätte auch nach 15 Jahren Merkel an der Spitze der Partei, ein ganz altes Problem im Umgang mit Frauen.
+Tauber: Ich würde sagen, wir merken, dass Frauen an verschiedenen Stellen in unserer Gesellschaft – und das findet in Parteien sicherlich auch Raum – nach wie vor Diskriminierung erfahren und dass wir gut daran tun, in allen Bereichen unserer Gesellschaft – auch dort, wie es noch nicht der Fall ist – Frauen wirklich teilhaben zu lassen an Macht und Entscheidung.
+Und deswegen muss man über dieses Thema ganz allgemein sprechen.
+Und natürlich ist es nicht in Ordnung, wenn es stattfindet.
+" Ich habe weder dieses Papier in Auftrag gegeben, noch habe ich es geschrieben" Detjen: Und jetzt sind Sie konkret damit konfrontiert, dass sich Leute an einen Vorfall erinnern, der eine ganze Zeit zurückliegen soll – zehn Jahre.
+Und da erheben Parteifreundinnen den Vorwurf, Sie seien an einem – so wie sich das liest – ziemlich fiesen Mobbing gegen die Geschäftsführerin Ihres hessischen Kreisverbandes Main-Kinzig beteiligt gewesen.
+Tauber: Ja, dazu habe ich an anderer Stelle schon alles gesagt.
+Das ist ein Vorgang, der elf Jahre zurückliegt.
+Ich habe weder dieses Papier in Auftrag gegeben, noch habe ich es geschrieben.
+Alle anderen Protagonisten sind nicht mehr in Amt und Würden.
+Die Dame war unter meiner Ägide auch Kreisgeschäftsführerin weiterhin, bis zu ihrer Pensionierung.
+Ich mag solche persönlichen Dinge, ehrlich gesagt, dann nicht weiter kommentieren.
+Sie muss selber wissen, was sie da umtreibt.
+Detjen: Aber Sie erinnern sich an den Vorfall, an dieses Papier?
+Tauber: Wissen Sie, damals hatten viele davon Kenntnis, auch das habe ich schon gesagt.
+Ich war nicht beteiligt am Schreiben des Papiers, ich bin nicht der Auftraggeber und ich habe eine leise Ahnung, warum das kurz vor meiner Nominierung aus der Schublade gezogen wird.
+Detjen: Gibt es etwas, was Sie da rückblickend bedauern?
+Tauber: Da ich es nicht geschrieben habe, habe ich mir da nichts vorzuwerfen.
+Detjen: Herr Tauber, wir haben über Angela Merkel und ihre bevorstehende vielleicht schon getroffene aber noch nicht verkündete Entscheidung gesprochen.
+Ist der CDU-Parteitag Anfang Dezember das, was Angela Merkel den " gegebenen Zeitpunkt" nennt?
+Tauber: Auch da gilt das, was die Vorsitzende immer sagt: Zu gegebener Zeit wird sie es uns wissen lassen, ob sie diesen Zeitpunkt für den gegebenen hält.
+Detjen: Wird der CSU-Vorsitzende, Horst Seehofer, beim CDU-Parteitag – so wie das Tradition ist bei den Unionsparteien – als Gastredner sprechen?
+Tauber: Wissen Sie, erstens sind die Einladungen noch nicht verschickt beiderseitig – auch darüber reden die beiden Vorsitzenden zusammen – und das Wichtige – und auch da sind wir uns jetzt wieder einig – ist natürlich auch die gemeinsame inhaltliche Basis.
+Und über die sprechen wir jetzt im Vorfeld auf den Deutschlandkongress, um dann auch mit Blick ins neue Jahr zu entscheiden, wie die gemeinsame Aufstellung fürs Bundestagswahlprogramm und für den Wahlkampf selbst aussieht.
+Detjen: Die Frage dränge ich Ihnen aber ja nicht auf, denn sie ist von Horst Seehofer aufgeworfen, der schon angekündigt hat, dass er Angela Merkel nicht auf dem CSU-Parteitag sehen will.
+Ist das inzwischen geklärt?
+Tauber: Das habe ich so nicht gehört, muss ich Ihnen ehrlich sagen.
+Detjen: So musste man es verstehen.
+Tauber: Ja, aber da weiß ich nicht, ob ich Ihrer Interpretation folgen möchte.
+Detjen: Ist es denn geklärt?
+Die Spitzen der Parteien haben ja jetzt viel miteinander gesprochen.
+Wir sitzen ja gerade in Würzburg, da gab es eine Veranstaltung beider Parteien, da kommen wir sicherlich auch gleich noch drauf zu sprechen.
+Aber zunächst nochmal die Frage: Ist oder wie weit ist das Verhältnis zwischen den beiden Vorsitzenden geklärt?
+Tauber: Wir hatten eine wirklich konstruktive, gute Sitzung am Ende der Woche und haben in der Woche ja auch andere Themen auf den Weg gebracht.
+Bei der Erbschaftssteuer haben wir jetzt ein Ergebnis, jetzt ist die nächste große Aufgabe das Thema Bund-Länder-Finanzen.
+Also, ich glaube, damit wird deutlich, wir schauen da nach vorne und wir lösen die Aufgaben.
+Detjen: Trotzdem noch einmal die Frage: Ist das Verhältnis oder wie weit ist das Verhältnis zwischen den Vorsitzenden der Parteien geklärt nach den letzten Begegnungen, das die Parteien ja bis in die Tiefe, bis in die Breite der Basis hinein belastet hat?
+Das ist auch hier in Würzburg ja nochmal deutlich geworden.
+Tauber: Ja, das war zu spüren in den gemeinsamen Veranstaltungen und Terminen, dass wir uns sehr darum bemühen, Antworten zu geben auf diese Fragen, die aktuellen – ich habe das Thema Erbschaftssteuer, das lange im Raum stand, genannt.
+Wir reden jetzt über die anderen noch offenen Punkte, auch die, die wir in der Koalition gemeinsam mit der SPD auf den Weg bringen wollen und müssen.
+Auch da ist es ja so, dass zum Beispiel beim Thema Freihandel die Union sich einig ist: Wir wollen eine starke Wirtschaft, wir wollen alles tun für Arbeitsplätze, wir müssen aber gucken, dass wir das gut tun und dass wir deutsche und europäische Interessen da einbringen – da verhält sich Sigmar Gabriel ein bisschen anders.
+Also, am Ende des Tages sehe ich, dass die Gemeinsamkeiten sehr stark sind.
+Dass wir auch immer Unterschiede haben, ist aber nichts Neues, nur, ich glaube, man merkt einfach, die sind nicht so groß, wie sie manchmal gemacht worden sind.
+" Dass wir eine europäische Lösung brauchen, um die Außengrenze zu schützen, auch da haben wir gar keinen Dissens" Detjen: Herr Tauber, ich habe jetzt beobachtet hier in Würzburg, das Treffen.
+Da wird über Gemeinsamkeiten besprochen, aber es ist doch nach wie vor vollkommen unübersehbar, wie groß die Hürden auch sind, wie groß die trennenden Fragen sind in der Flüchtlingspolitik und namentlich auch die Feindseligkeit – man kann das gar nicht anders sagen –, die Angela Merkel entgegentritt.
+Da tritt ja jemand auf und sagt also: 'Wenn eine Partei vom Abstieg bedroht ist, dann ist das wie im Fußball, dann muss der Trainer ausgewechselt werden' - und da gibt es Applaus im Saal.
+Tauber: Schauen Sie, wir sind uns bei den zentralen Fragen einig.
+Wir haben darüber geredet.
+Wir wollen, dass geltendes Recht umgesetzt wird.
+Und der Eindruck ist eben im letzten Jahr entstanden, dass das nicht ausreichend geschah.
+Da gibt es überhaupt keinen Dissens zwischen CDU und CSU, dass wir das Notwendige tun müssen, damit wir wissen, wer ist im Land.
+Das ist das Erste.
+Das Zweite, wir müssen dringend unterscheiden zwischen Asyl und Flucht und Einwanderungen auf der anderen Seite.
+Deswegen muss klar sein, wenn Asyl- und Fluchtgrund entfallen sind, muss derjenige Deutschland verlassen, es kann keinen dauerhaften Aufenthaltstitel geben.
+Dass man, wenn man hierherkommt um hier zu arbeiten, Integrationskurs durchlaufen muss, Sprachkurs absolvieren muss, auch da gibt es überhaupt keinen Dissens zwischen den beiden Unionsparteien.
+Dass wir eine europäische Lösung brauchen, um die Außengrenze zu schützen, auch da haben wir gar keinen Dissens.
+Wir streiten darum, wie wir weiterkommen können bei der Frage einer Begrenzung, ob es dafür eine Obergrenze braucht oder ob wir dafür andere Mechanismen finden, ob wir an diesem Wort festhalten müssen, da gibt es Bewegung in der Diskussion, das haben Sie gemerkt.
+Und da sind wir eben in einem Gespräch.
+Aber die Gemeinsamkeiten, die sind sehr, sehr groß, gerade auch bei dem Flüchtlingsthema.
+Detjen: Welche Bewegung gibt es da in der Diskussion?
+Da wird von anderen Begrifflichkeiten gesprochen.
+Bewegt man sich dann aber, was Zahlen, Kontingente, Obergrenzen angeht, aufeinander zu?
+Ist das die Lösung, dass man für das, was bisher Obergrenze genannt wird, den Begriff Richtgröße, Kontingent verwendet und dann ist das die Einigung?
+Tauber: Schauen Sie, wenn klar ist, dass jemand, der als Asylbewerber und Flüchtling zu uns kommt, nicht auf Dauer bleiben kann, sondern dass er nach Entfallen des Fluchtgrundes wieder gehen muss, es sei denn er erfüllt eine große Zahl von Voraussetzungen – eben den Integrationskurs, Sprachkurs, andere Dinge, einen Arbeitsplatz –, dann kann man natürlich darüber reden, ob diejenigen, die einwandern ins Land, ob man da sagt: Da verständigen wir uns auf eine bestimmte Zahl.
+Ich glaube aber, dass diese Zahl sich daran orientieren muss, welchen Bedarf hat unser Land, was brauchen wir an Einwanderung für unsere Volkswirtschaft, für den Fachkräftemangel.
+Da wird man nicht eine starre Zahl festlegen können, sondern da wird man das individuell überlegen müssen.
+Und auch da gibt es überhaupt keinen Dissens zwischen CDU und CSU, dass diese Zahl sich nach den Interessen unseres Landes orientieren muss, wenn wir über Zuwanderung reden.
+Detjen: Sie waren ja einer der Ersten in Ihrer Parteienfamilie, der sich schon vor der Zuspitzung der Flucht- und Migrationskrise im letzten Jahr stark dafür gemacht hat, ein Einwanderungsgesetz in Deutschland zu erlassen.
+Wenn ich Sie richtig verstehe, ist diese Überlegung für Sie nach wie vor und vielleicht mehr denn je aktuell?
+Tauber: Die CDU hat dazu eine Beschlusslage.
+Wir wollen die bestehenden Regeln in einem Gesetz zusammenführen – ich streite mich nicht über den genauen Namen.
+Und die CSU hat jetzt auch einen Beschluss gefasst, sie ist für ein Einwanderungsbegrenzungsgesetz – auch da streite ich mich nicht über den Namen.
+Aber wenn man gemeinsam aufschreibt und Regeln festlegt, unter welchen Voraussetzungen Menschen nach Deutschland kommen können, um hier zu leben und zu arbeiten, dann finde ich das einen guten Ansatz.
+Und auch da merkt man, offensichtlich sind wir auf dem Weg zu Gemeinsamkeiten da ein gutes Stück vorangekommen.
+Detjen: Sie haben auch bei dieser gemeinsamen Veranstaltung hier in Würzburg – die hieß " Deutschlandkongress" – über Gesellschaftspolitik über Integrationsfragen gesprochen.
+Der schwerste Vorwurf, der noch vor einem Jahr aus der CSU gegen die Bundeskanzlerin zu hören war, wurde immer so formuliert: " Die Bundeskanzlerin Angela Merkel will ein anderes Land" .
+Jetzt sagt Angela Merkel selbst in ihrer Haushaltsrede: Deutschland bleibt Deutschland – mit allem, was uns lieb und teuer ist.
+Aber die Frage ist ja: Was ist der CDU, was ist der Union lieb und teuer und ist es das Gleiche?
+Tauber: Sie hat gesagt: Deutschland wird Deutschland bleiben – mit allem, was uns lieb und teuer ist, und niemand wird trotzdem bestreiten, dass sich unser Land seit 1945 verändert hat und zwar sehr zum Positiven.
+Und jetzt geht es um die Frage – darüber haben wir ja geredet unter dem Stichwort " Leitkultur" , unter dem Stichwort " Wertebasis" , aber auch, wie ich finde, unter dem sehr spannenden Stichwort " Wertekenntnis" –, was setzt das denn voraus?
+Ist es nur das Grundgesetz?
+Nein.
+Sondern es sind Regeln des Umgangs miteinander, es sind kulturelle Fragen, es ist die Akzeptanz von Unterschieden, es ist die Neugier aufeinander, es ist der Respekt, es ist der Fleiß, es ist die Bereitschaft, Verantwortung zu übernehmen.
+Und sicherlich in einer pluralistischen Gesellschaft wird es auch Werte geben, die ich jetzt nicht aufgezählt habe, die andere für sich sehr wichtig finden.
+Und da gibt es in den beiden Unionsparteien wegen des " C" eine ganz große Übereinstimmung, ohne dass wir den Anspruch erheben, dass die Werte, die wir für wichtig erachten, die alleingültigen sind.
+Detjen: Haben Sie sich gefragt, ob das noch gilt, als Sie das Zitat Ihres Kollegen, des Generalsekretärs der CSU, Andreas Scheuer, gehört haben, der von ministrierenden Senegalesen spricht, die besonders schlimm sind, weil man sie nicht mehr abschieben kann?
+Tauber: Also ich finde, Andi Scheuer hat es verdient, dass man ihm da mal zuhört, wie es dazu gekommen ist.
+Und er sagt ja selbst, er empfindet, dass das Zitat aus dem Zusammenhang gerissen und verkürzt ist.
+Und ich finde, reden Sie mit ihm nochmal darüber.
+Detjen: Aber Herr Tauber, es ist klar, das hat Gauland, als er über Boateng gesprochen hat … Tauber: … ja, Entschuldigung.
+" Ich hätte es auch so nicht formuliert" Detjen: Also, so ein Zitat ...
+ich kann es ja nochmal vorlesen: " Das Schlimmste ist ein fußballspielender, ministrierender Senegalese, der über drei Jahre da ist, weil den wirst du nie wieder abschieben." Das ist blanker Rassismus, auch wenn man vorher augenzwinkernd sich für die Sprache entschuldigt.
+Tauber: Nein, ich bin jetzt nicht derjenige, der Andi Scheuer erklären muss, wie gesagt, das muss er selber tun.
+Ich hätte es auch so nicht formuliert.
+Aber die Frage, die dahintersteht, ist eben eine andere.
+Es geht um die Frage: Warum haben wir denn so große Probleme bei der Umsetzung des Asylrechts in den vergangenen Jahren?
+Wie kann es sein, dass Menschen lange hier sind, keinen geklärten Status haben?
+Warum haben wir bei den Verfahren so lange gebraucht?
+Und da müssen wir eben auch besser werden.
+Detjen: Aber das ist ja dann eine Frage an Ihre Parteien.
+Ist es, wenn man nicht sagt schlimm, ist es bedauernswert, ist es erstrebenswert, dass man Menschen, die lange hier sind, bestens integriert sind, dass man die abschiebt?
+Tauber: Das ist ja die Erfahrung der letzten Jahre.
+Wir haben in den letzten Jahren viele Fälle gehabt, wo Menschen eben lange auf eine Entscheidung des Bundesamtes für Migration und Flüchtlinge warten mussten, wo vor Ort schon unheimlich viel an Integrationsmaßnahmen stattgefunden hat und wo dann in der Tat aufgrund der Länge der Zeit auch entschieden wurde: Nein, entgegen der Rechtslage – sie müssten eigentlich gehen – dürfen sie bleiben.
+Und ich finde, das ist den Menschen gegenüber nicht fair und es ist eben nicht das, was – wie ich finde zu Recht – die Menschen bei uns im Land auch erwarten können, dass Regeln die da sind, eingehalten werden.
+Und deswegen ist es ja so wichtig, dass hier Verfahren beschleunigt werden, damit derjenige, der zu uns kommt, klar weiß, worauf er sich einlässt.
+Hat er eine Bleibeperspektive, dann lernt er die Sprache, macht einen Integrationskurs oder wird er gleich wieder gehen müssen.
+Und das ist ja ein Teil der Debatte: Warum ist es uns nicht gelungen in den letzten Jahren, das entsprechend aufzubauen.
+Und da leisten Frank-Jürgen Weise im BAMF und viele an anderer Stelle eben auch gute Arbeit, damit wir da besser werden.
+" Die Wahrheit ist auch, dass in den letzten Jahren wir auch viele andere Baustellen hatten" Detjen: Die Frage ist aber auch: Warum ist es nicht gelungen, auch in der Union nicht gelungen, die Diskussion, die Sie angestoßen haben, schon längst viel weiter voranzutreiben?
+Angela Merkel hat ja in ihrer Stellungnahme nach der Landeswahl von Berlin von Versäumnissen gesprochen, die auch etwas damit zu tun haben, gar nicht auf das letzte Jahr bezogen, sondern sich darauf bezogen haben, man hätte sich schon viel, viel früher – " viele, viele Jahre" , sagte sie – viel mehr auf die Migrationsströme, auf mögliche Fluchtströme vorbereiten können.
+Tauber: Ich finde, einerseits ist es doch gut, wenn wir darüber reden, haben wir auch Sachen falsch gemacht.
+Den Eindruck zu erwecken, es war immer alles richtig, den sollte keiner erheben.
+Die Wahrheit ist auch, dass in den letzten Jahren wir auch viele andere Baustellen hatten.
+Es ist ja nicht so, dass man einfach nur da im Bundestag saß und dachte: 'Na ja, gut, was fällt uns denn jetzt mal ein als Gesetz?
+' Sondern wir hatten die Staats- und Finanzkrise in der Welt – das war ein weltweites Ereignis – mit allen möglichen Auswirkungen, die wir teilweise ja bis heute spüren.
+Wir haben die Staatsschuldenkrise in Europa mit allen Folgen und Konsequenzen, die wir bis heute spüren.
+Wir erleben doch einfach, dass diese Welt sich verändert, dass Herausforderungen gar nicht mehr sozusagen lange schon am Horizont sichtbar sind, um sich darauf einzustellen, sondern dass man oft unmittelbar und schnell entscheiden und reagieren muss.
+Und dass dann noch hinzukommt, man ist noch gar nicht fertig mit dem einen Problem und schon kommt das nächste.
+Und deswegen finde ich es einerseits gut, nochmal zu überlegen: Hätten wir gewisse Entwicklungen früher sehen können?
+Dann kann man heute vielleicht auch nochmal den Blick auf andere Dinge richten.
+Das hilft aber nichts, die Probleme muss man eben jetzt lösen.
+Und man kann es eben nicht mehr rückwirkend tun.
+Deswegen, bleibe ich ja dabei, ist zum Beispiel das Abkommen mit der Türkei wichtig und es wäre noch wichtiger, wir hätten vergleichbare Abkommen auch mit anderen Ländern.
+Detjen: Angela Merkel hat gesagt, faktisch, da sind Fehler gemacht worden, sie wünschte sich, das Rad der Zeit zurückdrehen zu können.
+Die einen haben das so verstanden, dass sie Fehler in den zentralen Streitfragen ihrer Flüchtlingspolitik eingestanden hat.
+Wenn man genau zugehört hat, steht sie da aber hart zu dem, was im letzten Jahr gewesen ist.
+Hat sie sich da bewusst missverständlich ausgedrückt, sich auf die CSU zubewegt, wissend, dass sie in den Streitfragen aber die Position nicht räumt?
+Tauber: Na ja, also ich habe den Eindruck, dass das, was Angela Merkel da gesagt hat, natürlich in der Linie steht, die wir auf dem Parteitag in Karlsruhe beschlossen haben.
+Wir haben auf dem Parteitag sehr genau darüber diskutiert: Was ist jetzt eigentlich in den letzten Wochen und Monaten geschehen?
+Vor welchen Herausforderungen stehen wir da?
+Wie haben wir das bis jetzt bewältigt?
+Aber vor allem: Was ist jetzt noch zu tun?
+Und alle Entscheidungen, das Asylpaket I, das Asylpaket II, die Beschleunigung der Verfahren, die Unterstützung der Kommunen, die sicheren Herkunftsländer des Balkans, jetzt die Debatte um die sicheren Herkunftsländer Nordafrikas, all diese Dinge haben wir auf dem Parteitag diskutiert und beschlossen.
+Und ich muss Ihnen ehrlich sagen, ich habe ja schon viele Parteitage der CDU mitgemacht, ich kann mich an wenige erinnern, wo ein Beschluss gefasst wurde, der danach so wortnah umgesetzt wurde, Gesetzeskraft erlangt hat und jetzt eben – das ist das Nächste – auch einen Ausblick gegeben, was als Nächstes zu tun ist.
+Und das, finde ich, ist ihre Aufgabe als Kanzlerin.
+Detjen: Das Problem scheint mir zu sein – so schildern es auch viele Ihrer Parteifreunde –, dass man auf diese Maßnahmen verweisen kann, dass man auf Erfolge verweisen kann, es kommen nicht mehr so viele Flüchtlinge, man hat das Abkommen mit der Türkei geschlossen, das möglicherweise auch ein Modell für weitere Abkommen mit Mittelmeeranrainerstaaten sein kann und sein soll.
+Aber trotzdem stellt man dann fest, wenn man zur Basis geht, da hat es einen Vertrauensabriss gegeben, der sich auch in den jüngsten Wahlergebnissen niederschlägt, der ist so tief.
+Und dann hört man doch immer wieder den Zweifel und das Nachdenken darüber: Wie kriegen wir das eigentlich wieder in den Griff?
+Wie können wir dieses verlorene Vertrauen, da sich ja gerade auch an der Figur Angela Merkel festgemacht hat, wieder herstellen?
+Tauber: Wissen Sie, wir haben alle im letzten Herbst diesen Satz aufgegriffen: Das ist eine der größten Herausforderungen seit der Deutschen Einheit, vielleicht sogar noch weiter zurück.
+Und ich glaube, dass es ganz normal ist, wenn es wirklich so eine große Herausforderung war und ist, wenn es wirklich eine Krise war, dass Menschen dann erstmal zweifeln, ob sie wirklich gemeistert ist, ob das Problem wirklich gelöst ist.
+Und dann muss man sagen: Wir brauchen dafür manchmal auch noch Zeit.
+Manche Dinge gehen schneller.
+Die Zahl der Flüchtlinge zu reduzieren, das ging relativ schnell, aber den Nachweis zu erbringen, dass unsere Gesellschaft integrationsfähig ist und dass, wenn wir dann wissen, wer wirklich bleibt, wir diese Zahl der Menschen auch erfolgreich integrieren können, auch angesichts der Erfahrung in deutschen Städten von gescheiterter Integration, dass das Fragen sind, das finde ich sehr legitim.
+Und da muss die Politik eben nicht nur besser erklären, sondern sich zusätzlich auch fragen: Gibt es weitere Maßnahmen, die notwendig sind?
+Wie die sicheren Herkunftsländer Nordafrikas, wie auch die Frage: Tun wir schon genug in den Kommunen, um dort zu unterstützen bei der Integration?
+Diese Fragen und auch neue, an die wir heute noch gar nicht denken, werden sicherlich kommen.
+" Die Union tut gut daran, einerseits sich klar nach rechts abzugrenzen" Detjen: Jetzt manifestiert sich dieser Vertrauensabriss nicht nur für die CDU, aber in besonderer Weise für die CDU, auch im Erstarken einer anderen Partei, der AfD. Wir sind hier – ich habe es eben erwähnt – in Bayern, in Würzburg, wo Sie sich mit der CSU getroffen haben.
+CSU-Politiker verweisen darauf, dass die AfD in Bayern bei Umfragen deutlich schlechter abschneidet als im Rest Deutschlands und sie begründen damit dann auch nicht nur ihre Forderungen in der Sache, sondern auch – wir haben über Andreas Scheuer gesprochen – die zugespitzte Rhetorik.
+Was leiten Sie aus dieser Beobachtung mit Blick auf die Umfragen ab?
+Tauber: Ach, wenn ich an das Kommunalwahlergebnis in Niedersachsen denke, stelle ich auch fest, dass die AfD dort deutlich schlechter abgeschnitten hat als in Mecklenburg-Vorpommern oder jetzt auch in Berlin.
+Insofern glaube ich, dass jede Wahl und jedes Ergebnis auch seine eigenen Besonderheiten hat, wenn man sich Wählerwanderungen anschaut und so weiter.
+Ich glaube, die Union tut gut daran, einerseits sich klar nach rechts abzugrenzen – da hilft uns das " C" .
+Als Christdemokrat ist man Patriot aber eben wegen des " C" nie Nationalist.
+Und dann tun wir auch gut daran zu sagen: Wir dienen diesem Land seit 70 Jahren, wir lassen uns da jetzt auch nicht kirremachen, sondern wir arbeiten, wir haben gerade Verantwortung, wir tun das gemeinsam, und dazu dienen ja auch die Deutschlandkongresse, um das nach außen zu dokumentieren.
+Dass dabei die beiden Unionsparteien manchmal unterschiedlich sprechen und auch manchmal unterschiedliche Positionen haben, das ist auch normal – das war übrigens immer so in der Geschichte – und es ist ein bisschen auch unsere Stärke.
+Detjen: Herr Tauber, die nächste Wahl in Deutschland ist die Wahl des Bundespräsidenten am 12.
+Februar.
+Es heißt, man habe sich festgelegt in einem Spitzengespräch, einen gemeinsamen Kandidaten der Großen Koalition zu benennen.
+Ist das das Ziel?
+Tauber: Ich glaube, dass wir gute Erfahrungen damit gemacht haben, an der Spitze unseres Landes einen Menschen zu haben – einen Mann/eine Frau –, die gerade in Zeiten wie diesen in der Lage ist, Menschen zusammen zu bringen.
+Und wenn das eine der Voraussetzungen ist, dann tun die Parteien gut daran, möglichst zu zeigen, dass dieses Amt nicht im Parteienstreit vergeben wird.
+Detjen: Muss das neue Staatsoberhaupt – der Mann/die Frau –, das zwangsläufig in einer fünfjährigen Amtszeit des Bundespräsidenten auch mit Parteienstreit, mit Parteienpolitik konfrontiert ist, ein politischer Profi sein oder kann es auch ein Außenseiter sein?
+Tauber: Ich glaube oder lassen Sie mich es aus meiner Position als Generalsekretär beantworten, ich wünsche mir natürlich einen Präsidenten oder eine Präsidentin, die sagt: Dieses Land und unsere parlamentarische Demokratie braucht Parteien, braucht Menschen, die sich ehrenamtlich in Parteien engagieren, weil sonst diese Republik nicht funktionieren wird.
+Und bei allem Streit und auch allem Ärger und Unmut, den man über Parteien immer wieder artikulieren kann, zitiere ich einen Kollegen von Ihnen, der in der " FAZ" geschrieben hat: " Was Besseres als die Parteien, hat auch noch keiner erfunden, um politische Willensbildung zu organisieren." Und ich glaube in der Tat, neben einem Präsidenten, der Präsident für alle ist, wenn der zusätzlich noch das Signal aussendet: Unsere Demokratie braucht starke Parteien, dann wäre das ein schöner Anspruch, den ich an meinen künftigen oder meine künftige Präsidentin hätte.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周采访-260925-Fluchtlingspolitik</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Es ist uns gelungen, der Wahlkampf war erfolgreich.
+Detjen: Die Frage ist ja natürlich, ob Angela Merkel nochmal antritt.
+Und da sie immer darauf verweist, zum gegebenen Zeitpunkt - so formuliert sie immer - werde sie das sagen – wann auch immer das sein ist –, ist an Sie die Frage: Wünschen Sie sich, dass Angela Merkel nochmal antritt?
+Tauber: Also, ich kann Ihnen sagen, dass ich mir das persönlich natürlich wünsche und dass ich sehr froh bin, dass ich damit auch nicht alleine bin.
+Nicht nur in unserer Partei, sondern auch in unserem Land wünschen sich das viele.
+wissen, wie die Macht eines Bundeskanzlers aber auch eine Partei erodieren, verkrusten kann, wenn man 16 Jahre Bundeskanzler oder – so lange wäre sie am Ende einer vierten Amtszeit – Bundeskanzlerin， so verkrustet und verschlissen wäre, wie sie es einst unter Helmut Kohl war am Ende?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -803,16 +1005,36 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2035D850-8436-4AFB-930D-F4874D8EC37E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="336" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B42DA9-40FB-4B5C-864C-5AD944C8F030}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="26.58203125" customWidth="1"/>
+    <col min="4" max="4" width="24.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -822,8 +1044,11 @@
       <c r="C1" t="s">
         <v>7</v>
       </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -832,6 +1057,9 @@
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
